--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -73,7 +73,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -83,6 +83,13 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <x:si>
     <x:t>Num1</x:t>
   </x:si>
@@ -61,6 +61,9 @@
   </x:si>
   <x:si>
     <x:t>="Test" &amp; RC[-2] &amp; "R3C2"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TestAR3C2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Array Formula: </x:t>
@@ -450,7 +453,7 @@
     <x:col min="3" max="3" width="7.270625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="18.270625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="22.410625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.270625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.550625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="12.410625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -493,8 +496,8 @@
       <x:c r="E2" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>7</x:v>
+      <x:c r="F2" s="0" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G2" s="0">
         <x:f>IF(D2=F2,"Yes", "No")</x:f>
@@ -516,8 +519,8 @@
       <x:c r="E3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>9</x:v>
+      <x:c r="F3" s="0" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:f>IF(D3=F3,"Yes", "No")</x:f>
@@ -540,7 +543,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:f>IF(D4=F4,"Yes", "No")</x:f>
@@ -548,7 +551,7 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:f t="array" ref="B6">A2+A3</x:f>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -554,7 +554,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:f t="array" ref="B6">A2+A3</x:f>
+        <x:f t="array" ref="B6:B6">A2+A3</x:f>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -448,13 +448,13 @@
   <x:dimension ref="A1:G14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.410625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="8.270624999999999" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="7.270625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.270625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22.410625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.550625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.410625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.560625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.1106250000000006" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.2806250000000006" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20.190625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24.200625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.330625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.170625000000001" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -450,7 +450,7 @@
   <x:cols>
     <x:col min="1" max="1" width="14.560625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.1106250000000006" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.2806250000000006" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.020625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="20.190625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="24.200625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.330625" style="0" customWidth="1"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -134,19 +134,19 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Formulas.xlsx
@@ -449,12 +449,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.560625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.1106250000000006" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.110625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.020625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="20.190625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="24.200625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.330625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.170625000000001" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.170625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
